--- a/artfynd/A 11189-2023 artfynd.xlsx
+++ b/artfynd/A 11189-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589359</v>
+        <v>121589358</v>
       </c>
       <c r="B2" t="n">
-        <v>97065</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647543</v>
+        <v>647533</v>
       </c>
       <c r="R2" t="n">
-        <v>7167147</v>
+        <v>7167155</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshack på gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589358</v>
+        <v>121589360</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647533</v>
+        <v>647565</v>
       </c>
       <c r="R3" t="n">
-        <v>7167155</v>
+        <v>7167141</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack på gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589362</v>
+        <v>121589361</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>82393</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,30 +904,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647583</v>
+        <v>647576</v>
       </c>
       <c r="R4" t="n">
-        <v>7167093</v>
+        <v>7167083</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589364</v>
+        <v>121589362</v>
       </c>
       <c r="B5" t="n">
-        <v>92024</v>
+        <v>91996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,30 +1010,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647603</v>
+        <v>647583</v>
       </c>
       <c r="R5" t="n">
-        <v>7167092</v>
+        <v>7167093</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589365</v>
+        <v>121589364</v>
       </c>
       <c r="B7" t="n">
-        <v>74715</v>
+        <v>92024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,41 +1226,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647607</v>
+        <v>647603</v>
       </c>
       <c r="R7" t="n">
-        <v>7167059</v>
+        <v>7167092</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1295,18 +1292,12 @@
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal gran längs med bäck</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1325,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589361</v>
+        <v>121589359</v>
       </c>
       <c r="B8" t="n">
-        <v>82393</v>
+        <v>97065</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1369,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>647576</v>
+        <v>647543</v>
       </c>
       <c r="R8" t="n">
-        <v>7167083</v>
+        <v>7167147</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1431,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589360</v>
+        <v>121589365</v>
       </c>
       <c r="B9" t="n">
-        <v>91996</v>
+        <v>74715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1469,16 +1460,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>647565</v>
+        <v>647607</v>
       </c>
       <c r="R9" t="n">
-        <v>7167141</v>
+        <v>7167059</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1513,12 +1507,18 @@
           <t>2024-08-13</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gammal gran längs med bäck</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11189-2023 artfynd.xlsx
+++ b/artfynd/A 11189-2023 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589360</v>
+        <v>121589361</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>82393</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647565</v>
+        <v>647576</v>
       </c>
       <c r="R3" t="n">
-        <v>7167141</v>
+        <v>7167083</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589361</v>
+        <v>121589363</v>
       </c>
       <c r="B4" t="n">
-        <v>82393</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,30 +904,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647576</v>
+        <v>647603</v>
       </c>
       <c r="R4" t="n">
-        <v>7167083</v>
+        <v>7167092</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589362</v>
+        <v>121589359</v>
       </c>
       <c r="B5" t="n">
-        <v>91996</v>
+        <v>97065</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,26 +1014,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647583</v>
+        <v>647543</v>
       </c>
       <c r="R5" t="n">
-        <v>7167093</v>
+        <v>7167147</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589363</v>
+        <v>121589362</v>
       </c>
       <c r="B6" t="n">
         <v>91996</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647603</v>
+        <v>647583</v>
       </c>
       <c r="R6" t="n">
-        <v>7167092</v>
+        <v>7167093</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589359</v>
+        <v>121589360</v>
       </c>
       <c r="B8" t="n">
-        <v>97065</v>
+        <v>91996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>647543</v>
+        <v>647565</v>
       </c>
       <c r="R8" t="n">
-        <v>7167147</v>
+        <v>7167141</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 11189-2023 artfynd.xlsx
+++ b/artfynd/A 11189-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589358</v>
+        <v>121589364</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>92032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647533</v>
+        <v>647603</v>
       </c>
       <c r="R2" t="n">
-        <v>7167155</v>
+        <v>7167092</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshack på gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589361</v>
+        <v>121589358</v>
       </c>
       <c r="B3" t="n">
-        <v>82393</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647576</v>
+        <v>647533</v>
       </c>
       <c r="R3" t="n">
-        <v>7167083</v>
+        <v>7167155</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,6 +861,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack på gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +895,7 @@
         <v>121589363</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>92004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589359</v>
+        <v>121589360</v>
       </c>
       <c r="B5" t="n">
-        <v>97065</v>
+        <v>92004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647543</v>
+        <v>647565</v>
       </c>
       <c r="R5" t="n">
-        <v>7167147</v>
+        <v>7167141</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1107,7 @@
         <v>121589362</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>92004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589364</v>
+        <v>121589365</v>
       </c>
       <c r="B7" t="n">
-        <v>92024</v>
+        <v>74722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,38 +1226,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647603</v>
+        <v>647607</v>
       </c>
       <c r="R7" t="n">
-        <v>7167092</v>
+        <v>7167059</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,12 +1295,18 @@
           <t>2024-08-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal gran längs med bäck</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1316,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589360</v>
+        <v>121589359</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>97073</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1360,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>647565</v>
+        <v>647543</v>
       </c>
       <c r="R8" t="n">
-        <v>7167141</v>
+        <v>7167147</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589365</v>
+        <v>121589361</v>
       </c>
       <c r="B9" t="n">
-        <v>74715</v>
+        <v>82400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1447,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1460,19 +1469,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>647607</v>
+        <v>647576</v>
       </c>
       <c r="R9" t="n">
-        <v>7167059</v>
+        <v>7167083</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,18 +1513,12 @@
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gammal gran längs med bäck</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11189-2023 artfynd.xlsx
+++ b/artfynd/A 11189-2023 artfynd.xlsx
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589359</v>
+        <v>121589361</v>
       </c>
       <c r="B8" t="n">
-        <v>97073</v>
+        <v>82400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,25 +1337,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>647543</v>
+        <v>647576</v>
       </c>
       <c r="R8" t="n">
-        <v>7167147</v>
+        <v>7167083</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589361</v>
+        <v>121589359</v>
       </c>
       <c r="B9" t="n">
-        <v>82400</v>
+        <v>97073</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,25 +1443,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>647576</v>
+        <v>647543</v>
       </c>
       <c r="R9" t="n">
-        <v>7167083</v>
+        <v>7167147</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 11189-2023 artfynd.xlsx
+++ b/artfynd/A 11189-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589365</v>
+        <v>121589362</v>
       </c>
       <c r="B2" t="n">
-        <v>74722</v>
+        <v>92004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647607</v>
+        <v>647583</v>
       </c>
       <c r="R2" t="n">
-        <v>7167059</v>
+        <v>7167093</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,18 +757,12 @@
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal gran längs med bäck</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -896,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589360</v>
+        <v>121589358</v>
       </c>
       <c r="B4" t="n">
-        <v>92004</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647565</v>
+        <v>647533</v>
       </c>
       <c r="R4" t="n">
-        <v>7167141</v>
+        <v>7167155</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack på gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589361</v>
+        <v>121589359</v>
       </c>
       <c r="B5" t="n">
-        <v>82400</v>
+        <v>97073</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1046,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647576</v>
+        <v>647543</v>
       </c>
       <c r="R5" t="n">
-        <v>7167083</v>
+        <v>7167147</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589358</v>
+        <v>121589365</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>74722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1146,16 +1142,19 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647533</v>
+        <v>647607</v>
       </c>
       <c r="R6" t="n">
-        <v>7167155</v>
+        <v>7167059</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1192,7 +1191,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Födosökshack på gammalt talltorrträd</t>
+          <t>På gammal gran längs med bäck</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,6 +1200,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589362</v>
+        <v>121589360</v>
       </c>
       <c r="B7" t="n">
         <v>92004</v>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647583</v>
+        <v>647565</v>
       </c>
       <c r="R7" t="n">
-        <v>7167093</v>
+        <v>7167141</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589359</v>
+        <v>121589363</v>
       </c>
       <c r="B8" t="n">
-        <v>97073</v>
+        <v>92004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,26 +1341,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>647543</v>
+        <v>647603</v>
       </c>
       <c r="R8" t="n">
-        <v>7167147</v>
+        <v>7167092</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589363</v>
+        <v>121589361</v>
       </c>
       <c r="B9" t="n">
-        <v>92004</v>
+        <v>82400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,30 +1443,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>647603</v>
+        <v>647576</v>
       </c>
       <c r="R9" t="n">
-        <v>7167092</v>
+        <v>7167083</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 11189-2023 artfynd.xlsx
+++ b/artfynd/A 11189-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589362</v>
+        <v>121589359</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>97073</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647583</v>
+        <v>647543</v>
       </c>
       <c r="R2" t="n">
-        <v>7167093</v>
+        <v>7167147</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589364</v>
+        <v>121589365</v>
       </c>
       <c r="B3" t="n">
-        <v>92032</v>
+        <v>74722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,38 +797,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647603</v>
+        <v>647607</v>
       </c>
       <c r="R3" t="n">
-        <v>7167092</v>
+        <v>7167059</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,12 +866,18 @@
           <t>2024-08-13</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal gran längs med bäck</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589358</v>
+        <v>121589363</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>92004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +908,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647533</v>
+        <v>647603</v>
       </c>
       <c r="R4" t="n">
-        <v>7167155</v>
+        <v>7167092</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,11 +976,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosökshack på gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589359</v>
+        <v>121589360</v>
       </c>
       <c r="B5" t="n">
-        <v>97073</v>
+        <v>92004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647543</v>
+        <v>647565</v>
       </c>
       <c r="R5" t="n">
-        <v>7167147</v>
+        <v>7167141</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121589365</v>
+        <v>121589364</v>
       </c>
       <c r="B6" t="n">
-        <v>74722</v>
+        <v>92032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,41 +1124,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647607</v>
+        <v>647603</v>
       </c>
       <c r="R6" t="n">
-        <v>7167059</v>
+        <v>7167092</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,18 +1190,12 @@
           <t>2024-08-13</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal gran längs med bäck</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1219,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121589360</v>
+        <v>121589361</v>
       </c>
       <c r="B7" t="n">
-        <v>92004</v>
+        <v>82400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,25 +1226,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1263,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>647565</v>
+        <v>647576</v>
       </c>
       <c r="R7" t="n">
-        <v>7167141</v>
+        <v>7167083</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,7 +1320,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121589363</v>
+        <v>121589362</v>
       </c>
       <c r="B8" t="n">
         <v>92004</v>
@@ -1360,7 +1355,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1369,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>647603</v>
+        <v>647583</v>
       </c>
       <c r="R8" t="n">
-        <v>7167092</v>
+        <v>7167093</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1431,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121589361</v>
+        <v>121589358</v>
       </c>
       <c r="B9" t="n">
-        <v>82400</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,21 +1442,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1475,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>647576</v>
+        <v>647533</v>
       </c>
       <c r="R9" t="n">
-        <v>7167083</v>
+        <v>7167155</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1511,6 +1506,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosökshack på gammalt talltorrträd</t>
         </is>
       </c>
       <c r="AD9" t="b">
